--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -1432,11 +1432,11 @@
         <v>116904015</v>
       </c>
       <c r="B8" t="n">
-        <v>56239</v>
+        <v>56432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>116904015</v>
       </c>
       <c r="B8" t="n">
-        <v>56432</v>
+        <v>56435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -821,12 +821,7 @@
         <v>108735526</v>
       </c>
       <c r="B3" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -821,7 +821,7 @@
         <v>108735526</v>
       </c>
       <c r="B3" t="n">
-        <v>56817</v>
+        <v>56818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116904161</v>
+        <v>111739362</v>
       </c>
       <c r="B2" t="n">
-        <v>56236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>100041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,17 +713,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -736,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kostad, Finnspång, Ög</t>
+          <t>Melby, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554707</v>
+        <v>554727</v>
       </c>
       <c r="R2" t="n">
-        <v>6505113</v>
+        <v>6505022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,27 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under stock.</t>
+          <t>Observatör: Roger Johansson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,12 +783,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -821,7 +798,7 @@
         <v>108735526</v>
       </c>
       <c r="B3" t="n">
-        <v>56840</v>
+        <v>56899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -960,32 +937,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114462190</v>
+        <v>116904015</v>
       </c>
       <c r="B4" t="n">
-        <v>56223</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -998,28 +970,44 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolstad, Ög</t>
+          <t>Kolstad, Finnspång, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554790</v>
+        <v>554882</v>
       </c>
       <c r="R4" t="n">
-        <v>6505155</v>
+        <v>6504940</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,12 +1031,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Individen som sågs hade återbildad svans. Prassel av ytterligare två individer hördes.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,27 +1067,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ogun Caglayan Turkay</t>
+          <t>Vide Ohlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ogun Caglayan Turkay</t>
+          <t>Vide Ohlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114462251</v>
+        <v>114462278</v>
       </c>
       <c r="B5" t="n">
-        <v>56223</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,21 +1090,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208257</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1117,7 +1115,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1129,10 +1127,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554828</v>
+        <v>554819</v>
       </c>
       <c r="R5" t="n">
-        <v>6505083</v>
+        <v>6505047</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1159,12 +1157,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,15 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114462278</v>
+        <v>116904119</v>
       </c>
       <c r="B6" t="n">
-        <v>58050</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,50 +1201,62 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>208255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolstad, Ög</t>
+          <t>Kolstad, Finnspång, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554819</v>
+        <v>554971</v>
       </c>
       <c r="R6" t="n">
-        <v>6505047</v>
+        <v>6504908</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,12 +1280,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,27 +1311,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ogun Caglayan Turkay</t>
+          <t>Vide Ohlin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ogun Caglayan Turkay</t>
+          <t>Vide Ohlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114462223</v>
+        <v>114462190</v>
       </c>
       <c r="B7" t="n">
-        <v>56223</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1359,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554828</v>
+        <v>554790</v>
       </c>
       <c r="R7" t="n">
-        <v>6505084</v>
+        <v>6505155</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,12 +1401,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,32 +1434,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116904015</v>
+        <v>114462223</v>
       </c>
       <c r="B8" t="n">
-        <v>56435</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100070</v>
+        <v>208257</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1462,44 +1467,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolstad, Finnspång, Ög</t>
+          <t>Kolstad, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554882</v>
+        <v>554828</v>
       </c>
       <c r="R8" t="n">
-        <v>6504940</v>
+        <v>6505084</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,27 +1512,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Individen som sågs hade återbildad svans. Prassel av ytterligare två individer hördes.</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,27 +1533,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
+          <t>Ogun Caglayan Turkay</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
+          <t>Ogun Caglayan Turkay</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116904119</v>
+        <v>114462251</v>
       </c>
       <c r="B9" t="n">
-        <v>56244</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,62 +1556,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208255</v>
+        <v>208257</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolstad, Finnspång, Ög</t>
+          <t>Kolstad, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554971</v>
+        <v>554828</v>
       </c>
       <c r="R9" t="n">
-        <v>6504908</v>
+        <v>6505083</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1666,22 +1623,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,15 +1644,153 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Ogun Caglayan Turkay</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ogun Caglayan Turkay</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116904161</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kostad, Finnspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>554707</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6505113</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Under stock.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Vide Ohlin</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Vide Ohlin</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41742-2021 artfynd.xlsx
+++ b/artfynd/A 41742-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111739362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108735526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1076,6 +1091,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116904015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1187,6 +1207,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114462278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1320,6 +1345,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116904119</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1431,6 +1461,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114462190</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1542,6 +1577,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114462223</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1653,6 +1693,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114462251</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1791,8 +1836,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116904161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>